--- a/output/pdf_financials_xlsx/SII.xlsx
+++ b/output/pdf_financials_xlsx/SII.xlsx
@@ -889,52 +889,52 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>88.023</v>
+        <v>62.363</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>103.686</v>
+        <v>148.946</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>146.825</v>
+        <v>117.283</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>118.514</v>
+        <v>116.446</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>84.69799999999999</v>
+        <v>200.434</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>227230</v>
+        <v>96454</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>24922.371</v>
+        <v>156.985</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>113.805</v>
+        <v>129.344</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>47818</v>
+        <v>9057</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>47579</v>
+        <v>11433</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>45028</v>
+        <v>9057</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>118.606</v>
+        <v>119.455</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>131.333</v>
+        <v>120.103</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>148.815</v>
+        <v>101.076</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>174.111</v>
+        <v>109.649</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>217.441</v>
+        <v>194.724</v>
       </c>
     </row>
     <row r="11">
@@ -944,52 +944,52 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>19.502</v>
+        <v>45.162</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>219.815</v>
+        <v>174.555</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14.427</v>
+        <v>43.969</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>39.64</v>
+        <v>41.708</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>29.674</v>
+        <v>-86.062</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-102715</v>
+        <v>28061</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-24796.364</v>
+        <v>-30.978</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>53.382</v>
+        <v>37.843</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-14339</v>
+        <v>24422</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-15913</v>
+        <v>20233</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-11549</v>
+        <v>24422</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>46.039</v>
+        <v>45.19</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13.849</v>
+        <v>25.079</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>2.552</v>
+        <v>50.291</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>4.544</v>
+        <v>69.006</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>67.64100000000001</v>
+        <v>90.358</v>
       </c>
     </row>
     <row r="12">
@@ -1008,22 +1008,22 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>2.691</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>9.843999999999999</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>20184</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>18.714</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>14.162</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>15.593</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>13229</v>
@@ -1925,22 +1925,22 @@
         <v>43.969</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>41.708</v>
+        <v>39.017</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-86.062</v>
+        <v>-95.90600000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>28061</v>
+        <v>7877</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-30978</v>
+        <v>-30996.714</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>37.843</v>
+        <v>23.681</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>24422</v>
+        <v>24406.407</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>7004</v>
@@ -2035,10 +2035,10 @@
         <v>51.188</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>49.49</v>
+        <v>46.799</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-86.062</v>
+        <v>-95.90600000000001</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>37148</v>
@@ -2047,10 +2047,10 @@
         <v>19009</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>37.843</v>
+        <v>23.681</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>24422</v>
+        <v>24406.407</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>7004</v>
@@ -2090,10 +2090,10 @@
         <v>31.74410239872994</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>31.29228473513158</v>
+        <v>29.59077860819201</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-75.24743818417096</v>
+        <v>-83.8544398978771</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>29.83415652732602</v>
@@ -2102,10 +2102,10 @@
         <v>15085.66984373884</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>22.63513311441679</v>
+        <v>14.16437880935719</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>72.94722064577796</v>
+        <v>72.90064518056096</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>22.11836038653445</v>
@@ -48246,7 +48246,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -48626,7 +48626,7 @@
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E431" s="5" t="n">
@@ -53494,7 +53494,7 @@
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -55024,7 +55024,11 @@
           <t>Interest expense 39 —</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E499" t="inlineStr">
         <is>
           <t>-</t>
@@ -55310,7 +55314,7 @@
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
@@ -56262,7 +56266,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -56552,7 +56556,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -58538,7 +58542,7 @@
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -60256,7 +60260,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -61494,7 +61498,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -62436,7 +62440,7 @@
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
@@ -64852,7 +64856,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
@@ -66228,7 +66232,7 @@
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -66600,7 +66604,7 @@
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -71978,7 +71982,7 @@
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">

--- a/output/pdf_financials_xlsx/SII.xlsx
+++ b/output/pdf_financials_xlsx/SII.xlsx
@@ -2004,19 +2004,19 @@
         <v>0</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>3.622</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>3.355</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>2.221</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>2.477</v>
       </c>
     </row>
     <row r="29">
@@ -2059,19 +2059,19 @@
         <v>10538</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>41.655</v>
+        <v>45.277</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>20.088</v>
+        <v>23.443</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>43.8</v>
+        <v>46.643</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>60.097</v>
+        <v>62.318</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>83.696</v>
+        <v>86.173</v>
       </c>
     </row>
     <row r="30">
@@ -2114,19 +2114,19 @@
         <v>31.47644792257833</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>25.29988763703726</v>
+        <v>27.49977223723769</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>13.83642600322354</v>
+        <v>16.14731853811078</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>28.93629390818342</v>
+        <v>30.81451042829679</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>33.63857714589572</v>
+        <v>34.88175533850158</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>29.35857051655313</v>
+        <v>30.22744333209392</v>
       </c>
     </row>
     <row r="31">
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>7.219</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>7.782</v>
       </c>
       <c r="F100" s="3" t="n">
         <v>0</v>
@@ -6313,16 +6313,16 @@
         <v>0</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>3.355</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>2.843</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>2.221</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>2.477</v>
       </c>
     </row>
     <row r="101">
@@ -37088,7 +37088,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -45250,7 +45254,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -48336,7 +48340,11 @@
           <t>Depreciation of property and equipment (Note 8)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -50010,7 +50018,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
@@ -50746,7 +50758,11 @@
           <t>Depreciation of property and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
